--- a/artfynd/A 37207-2025 artfynd.xlsx
+++ b/artfynd/A 37207-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128322563</v>
       </c>
       <c r="B3" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37207-2025 artfynd.xlsx
+++ b/artfynd/A 37207-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128322563</v>
       </c>
       <c r="B3" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37207-2025 artfynd.xlsx
+++ b/artfynd/A 37207-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128322563</v>
       </c>
       <c r="B3" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37207-2025 artfynd.xlsx
+++ b/artfynd/A 37207-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128322563</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37207-2025 artfynd.xlsx
+++ b/artfynd/A 37207-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128322563</v>
       </c>
       <c r="B3" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37207-2025 artfynd.xlsx
+++ b/artfynd/A 37207-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128228760</v>
+        <v>128228764</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601601</v>
+        <v>601692</v>
       </c>
       <c r="R2" t="n">
-        <v>6825363</v>
+        <v>6825344</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128322563</v>
+        <v>128228761</v>
       </c>
       <c r="B3" t="n">
-        <v>57880</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,48 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mon, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601818</v>
+        <v>601554</v>
       </c>
       <c r="R3" t="n">
-        <v>6825381</v>
+        <v>6825379</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -848,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,15 +857,317 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Emma Hellkvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128228760</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mon, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>601601</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6825363</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emma Hellkvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128228763</v>
+      </c>
+      <c r="B5" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mon, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>601694</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6825351</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Hellkvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128322563</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mon, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>601818</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6825381</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Samuel Persson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Tore Dahlberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
